--- a/reports/pdf_rolling5_20261016.xlsx
+++ b/reports/pdf_rolling5_20261016.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,947억   ·   현금 615억(12.7%)      오늘 2026-10-16  vs  5일전 2026-10-08      매수 13종목  /  매도 30종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,418억   ·   현금 410억(8.9%)      오늘 2026-10-16  vs  5일전 2026-10-08      매수 13종목  /  매도 30종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>489</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>3461384822</v>
+        <v>3464883689</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-310</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2780512652</v>
+        <v>-2783323274</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>139</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>487827213</v>
+        <v>488320323</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-126</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1913510672</v>
+        <v>-1915444904</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>71</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>983356623</v>
+        <v>984350628</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-103</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1942527558</v>
+        <v>-1944491121</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>63</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>714136154</v>
+        <v>714858023</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-81</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1262991888</v>
+        <v>-1264268556</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>50</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3326398387</v>
+        <v>3329760806</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-79</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-2127310969</v>
+        <v>-2129461316</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>46</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1885355086</v>
+        <v>1887260857</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-74</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-3644683233</v>
+        <v>-3648367384</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>41</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>3036130528</v>
+        <v>3039199536</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-73</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1781454636</v>
+        <v>-1783255382</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>38</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1359962341</v>
+        <v>1361337030</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-71</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2910004589</v>
+        <v>-2912946105</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>32</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1319471360</v>
+        <v>1320805120</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>-35</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-864517081</v>
+        <v>-865390960</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>28</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1241855398</v>
+        <v>1243110701</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>-31</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-2958514566</v>
+        <v>-2961505117</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>950696539</v>
+        <v>951657530</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>-29</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-2187700939</v>
+        <v>-2189912330</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1535489256</v>
+        <v>1537041372</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>-26</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1469753287</v>
+        <v>-1471238956</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1259774389</v>
+        <v>1261047805</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>-23</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-901691563</v>
+        <v>-902603019</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>-21</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-810809607</v>
+        <v>-811629197</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>-20</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-924659552</v>
+        <v>-925594224</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>-16</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-325511842</v>
+        <v>-325840879</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>-15</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1844369106</v>
+        <v>-1846233447</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1352,23 +1352,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-378377817</v>
+        <v>-746817781</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.57%</t>
+          <t>0.31%→0.13%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>88→76</t>
+          <t>21→9</t>
         </is>
       </c>
     </row>
@@ -1380,23 +1380,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-468665773</v>
+        <v>-378760292</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.18%→0.11%</t>
+          <t>0.58%→0.57%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>24→12</t>
+          <t>88→76</t>
         </is>
       </c>
     </row>
@@ -1408,23 +1408,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-746063638</v>
+        <v>-469139514</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.31%→0.13%</t>
+          <t>0.18%→0.11%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>21→9</t>
+          <t>24→12</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         <v>-11</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-879911573</v>
+        <v>-880801013</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>-9</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1314224363</v>
+        <v>-1315552819</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1492,23 +1492,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-386693813</v>
+        <v>-1883395956</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.24%</t>
+          <t>2.79%→2.62%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>48→41</t>
         </is>
       </c>
     </row>
@@ -1520,23 +1520,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1881494088</v>
+        <v>-768619786</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2.79%→2.62%</t>
+          <t>1.27%→1.15%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>48→41</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1548,23 +1548,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-767843628</v>
+        <v>-387084694</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>1.27%→1.15%</t>
+          <t>0.33%→0.24%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
         <v>-6</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1214729411</v>
+        <v>-1215957294</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>-6</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-301157854</v>
+        <v>-301462273</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>-4</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-861299582</v>
+        <v>-862170209</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1660,23 +1660,23 @@
       <c r="E34" s="17" t="n"/>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-366200822</v>
+        <v>-1027171749</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>5.50%→5.22%</t>
+          <t>0.41%→0.16%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>5→2</t>
         </is>
       </c>
     </row>
@@ -1688,30 +1688,30 @@
       <c r="E35" s="17" t="n"/>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-1026134502</v>
+        <v>-366570989</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.16%</t>
+          <t>5.50%→5.22%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>5→2</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,990억   ·   현금 198억(6.6%)      오늘 2026-10-16  vs  5일전 2026-10-08      매수 2종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,871억   ·   현금 132억(4.5%)      오늘 2026-10-16  vs  5일전 2026-10-08      매수 2종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1807,7 +1807,7 @@
         <v>56</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1411284266</v>
+        <v>1411284586</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>-20</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-2740100517</v>
+        <v>-2740101137</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>51</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>825766656</v>
+        <v>825766843</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>-19</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-843866159</v>
+        <v>-843866350</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>-14</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-2864120540</v>
+        <v>-2864121189</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,556억   ·   현금 116억(5.0%)      오늘 2026-10-16  vs  5일전 2026-10-08      매수 8종목  /  매도 12종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,260억   ·   현금 77억(3.4%)      오늘 2026-10-16  vs  5일전 2026-10-08      매수 8종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B44" s="4" t="n"/>
@@ -2012,7 +2012,7 @@
         <v>45</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>5492107833</v>
+        <v>5483772333</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>-150</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-3914461307</v>
+        <v>-3908520238</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>36</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1594253332</v>
+        <v>1591833697</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>-96</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-1467725290</v>
+        <v>-1465497689</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>31</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1016343089</v>
+        <v>1014800562</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>-80</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-1491976498</v>
+        <v>-1489712091</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>21</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>2830076445</v>
+        <v>2825781172</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>-66</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-1237404713</v>
+        <v>-1235526675</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>19</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>626050209</v>
+        <v>625100038</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>-53</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-1311509288</v>
+        <v>-1309518780</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>14</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>745461049</v>
+        <v>744329645</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>-50</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-920952807</v>
+        <v>-919555056</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>14</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>1112655971</v>
+        <v>1110967268</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>-39</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-2243698049</v>
+        <v>-2240292736</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>13</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>3623842210</v>
+        <v>3618342220</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>-33</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-1183037195</v>
+        <v>-1181241672</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>-30</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-1486704496</v>
+        <v>-1484448090</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>-30</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-1354245452</v>
+        <v>-1352190082</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>-18</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-2532537845</v>
+        <v>-2528694154</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>-6</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1022109341</v>
+        <v>-1020558062</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,913억   ·   현금 122억(6.3%)      오늘 2026-10-16  vs  5일전 2026-10-08      매수 5종목  /  매도 10종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,855억   ·   현금 81억(4.3%)      오늘 2026-10-16  vs  5일전 2026-10-08      매수 5종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B60" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
         <v>229</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>15971443032</v>
+        <v>15971438028</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>-356</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-4165430965</v>
+        <v>-4165429660</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>125</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>1678018575</v>
+        <v>1678018049</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>-313</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-2895077548</v>
+        <v>-2895076641</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>58</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>905220405</v>
+        <v>905220122</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>-242</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-8091486955</v>
+        <v>-8091484420</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>53</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>823124364</v>
+        <v>823124106</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>-238</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-1873214504</v>
+        <v>-1873213917</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>15</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>7164014252</v>
+        <v>7164012007</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>-235</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-1867603555</v>
+        <v>-1867602970</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>-63</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-986875997</v>
+        <v>-986875688</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>-56</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-1797342212</v>
+        <v>-1797341649</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>-34</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-5026491475</v>
+        <v>-5026489900</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>-20</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-1635409829</v>
+        <v>-1635409317</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>-12</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-103869589</v>
+        <v>-103869557</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
     <row r="74" ht="19" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 296억   ·   현금 10억(3.3%)      오늘 2026-10-16  vs  5일전 2026-10-08      매수 6종목  /  매도 6종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 263억   ·   현금 7억(2.5%)      오늘 2026-10-16  vs  5일전 2026-10-08      매수 6종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B74" s="4" t="n"/>
@@ -3014,11 +3014,11 @@
         <v>42</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>12536370</v>
+        <v>12001703</v>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>2.61%→2.66%</t>
+          <t>2.81%→2.87%</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
@@ -3035,11 +3035,11 @@
         <v>-88</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>-67450240</v>
+        <v>-58901005</v>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>8.23%→8.02%</t>
+          <t>8.08%→7.87%</t>
         </is>
       </c>
       <c r="K77" s="13" t="inlineStr">
@@ -3058,11 +3058,11 @@
         <v>17</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>63897900</v>
+        <v>53191268</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>2.48%→2.70%</t>
+          <t>2.32%→2.53%</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
@@ -3079,11 +3079,11 @@
         <v>-52</v>
       </c>
       <c r="I78" s="15" t="n">
-        <v>-91629200</v>
+        <v>-82570751</v>
       </c>
       <c r="J78" s="16" t="inlineStr">
         <is>
-          <t>3.01%→2.71%</t>
+          <t>3.05%→2.74%</t>
         </is>
       </c>
       <c r="K78" s="13" t="inlineStr">
@@ -3102,11 +3102,11 @@
         <v>8</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>79006400</v>
+        <v>66088761</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>2.33%→2.60%</t>
+          <t>2.19%→2.45%</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
@@ -3123,11 +3123,11 @@
         <v>-32</v>
       </c>
       <c r="I79" s="15" t="n">
-        <v>-25406400</v>
+        <v>-23005106</v>
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>1.60%→1.52%</t>
+          <t>1.63%→1.54%</t>
         </is>
       </c>
       <c r="K79" s="13" t="inlineStr">
@@ -3146,11 +3146,11 @@
         <v>6</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>70028400</v>
+        <v>59294965</v>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>1.31%→1.56%</t>
+          <t>1.25%→1.48%</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
@@ -3167,11 +3167,11 @@
         <v>-13</v>
       </c>
       <c r="I80" s="15" t="n">
-        <v>-109920200</v>
+        <v>-105042537</v>
       </c>
       <c r="J80" s="16" t="inlineStr">
         <is>
-          <t>2.60%→2.23%</t>
+          <t>2.79%→2.39%</t>
         </is>
       </c>
       <c r="K80" s="13" t="inlineStr">
@@ -3190,11 +3190,11 @@
         <v>5</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>75207500</v>
+        <v>71522457</v>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>0.98%→1.23%</t>
+          <t>1.04%→1.32%</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
@@ -3211,11 +3211,11 @@
         <v>-12</v>
       </c>
       <c r="I81" s="15" t="n">
-        <v>-44059200</v>
+        <v>-39034177</v>
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>1.28%→1.13%</t>
+          <t>1.27%→1.13%</t>
         </is>
       </c>
       <c r="K81" s="13" t="inlineStr">
@@ -3234,11 +3234,11 @@
         <v>5</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>46498000</v>
+        <v>39697476</v>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>2.73%→2.89%</t>
+          <t>2.62%→2.78%</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr">
@@ -3255,11 +3255,11 @@
         <v>-5</v>
       </c>
       <c r="I82" s="15" t="n">
-        <v>-70015000</v>
+        <v>-62041963</v>
       </c>
       <c r="J82" s="16" t="inlineStr">
         <is>
-          <t>3.54%→3.31%</t>
+          <t>3.52%→3.29%</t>
         </is>
       </c>
       <c r="K82" s="13" t="inlineStr">
@@ -3288,7 +3288,7 @@
     <row r="86" ht="19" customHeight="1">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,035억      오늘 2026-10-16  vs  5일전 2026-10-08      매수 0종목  /  매도 0종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 994억      오늘 2026-10-16  vs  5일전 2026-10-08      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B86" s="4" t="n"/>

--- a/reports/pdf_rolling5_20261016.xlsx
+++ b/reports/pdf_rolling5_20261016.xlsx
@@ -1352,23 +1352,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-746817781</v>
+        <v>-469139514</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.31%→0.13%</t>
+          <t>0.18%→0.11%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>21→9</t>
+          <t>24→12</t>
         </is>
       </c>
     </row>
@@ -1408,23 +1408,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-469139514</v>
+        <v>-746817781</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.18%→0.11%</t>
+          <t>0.31%→0.13%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>24→12</t>
+          <t>21→9</t>
         </is>
       </c>
     </row>
@@ -1492,23 +1492,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1883395956</v>
+        <v>-387084694</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>2.79%→2.62%</t>
+          <t>0.33%→0.24%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>48→41</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>
@@ -1548,23 +1548,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-387084694</v>
+        <v>-1883395956</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.24%</t>
+          <t>2.79%→2.62%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>48→41</t>
         </is>
       </c>
     </row>
@@ -1576,23 +1576,23 @@
       <c r="E31" s="17" t="n"/>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>하나마이크론  (편출)</t>
         </is>
       </c>
       <c r="H31" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1215957294</v>
+        <v>-301462273</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>0.50%→0.24%</t>
+          <t>0.06%→0.00%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>11→5</t>
+          <t>6→0</t>
         </is>
       </c>
     </row>
@@ -1604,23 +1604,23 @@
       <c r="E32" s="17" t="n"/>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론  (편출)</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H32" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-301462273</v>
+        <v>-1215957294</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>0.06%→0.00%</t>
+          <t>0.50%→0.24%</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
         <is>
-          <t>6→0</t>
+          <t>11→5</t>
         </is>
       </c>
     </row>
@@ -1660,23 +1660,23 @@
       <c r="E34" s="17" t="n"/>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-1027171749</v>
+        <v>-366570989</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.16%</t>
+          <t>5.50%→5.22%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>5→2</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
@@ -1688,23 +1688,23 @@
       <c r="E35" s="17" t="n"/>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-366570989</v>
+        <v>-1027171749</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>5.50%→5.22%</t>
+          <t>0.41%→0.16%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>5→2</t>
         </is>
       </c>
     </row>
@@ -2225,23 +2225,23 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>744329645</v>
+        <v>1110967268</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>2.82%→3.42%</t>
+          <t>1.95%→3.18%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>129→143</t>
+          <t>75→89</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -2269,23 +2269,23 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>1110967268</v>
+        <v>744329645</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>1.95%→3.18%</t>
+          <t>2.82%→3.42%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>75→89</t>
+          <t>129→143</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -3183,23 +3183,23 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B81" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>71522457</v>
+        <v>39697476</v>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>1.04%→1.32%</t>
+          <t>2.62%→2.78%</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>19→24</t>
+          <t>86→91</t>
         </is>
       </c>
       <c r="G81" s="14" t="inlineStr">
@@ -3227,23 +3227,23 @@
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B82" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>39697476</v>
+        <v>71522457</v>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>2.62%→2.78%</t>
+          <t>1.04%→1.32%</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr">
         <is>
-          <t>86→91</t>
+          <t>19→24</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20261016.xlsx
+++ b/reports/pdf_rolling5_20261016.xlsx
@@ -1352,23 +1352,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-469139514</v>
+        <v>-746817781</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.18%→0.11%</t>
+          <t>0.31%→0.13%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>24→12</t>
+          <t>21→9</t>
         </is>
       </c>
     </row>
@@ -1408,23 +1408,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-746817781</v>
+        <v>-469139514</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.31%→0.13%</t>
+          <t>0.18%→0.11%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>21→9</t>
+          <t>24→12</t>
         </is>
       </c>
     </row>
@@ -1660,23 +1660,23 @@
       <c r="E34" s="17" t="n"/>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-366570989</v>
+        <v>-1027171749</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>5.50%→5.22%</t>
+          <t>0.41%→0.16%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>5→2</t>
         </is>
       </c>
     </row>
@@ -1688,23 +1688,23 @@
       <c r="E35" s="17" t="n"/>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-1027171749</v>
+        <v>-366570989</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.16%</t>
+          <t>5.50%→5.22%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>5→2</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
@@ -2225,23 +2225,23 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>1110967268</v>
+        <v>744329645</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>1.95%→3.18%</t>
+          <t>2.82%→3.42%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>75→89</t>
+          <t>129→143</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -2269,23 +2269,23 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>744329645</v>
+        <v>1110967268</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>2.82%→3.42%</t>
+          <t>1.95%→3.18%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>129→143</t>
+          <t>75→89</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -2362,18 +2362,18 @@
       <c r="E55" s="17" t="n"/>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>쎄트렉아이  (편출)</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-1484448090</v>
+        <v>-1352190082</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.54%→0.00%</t>
+          <t>0.49%→0.00%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2390,18 +2390,18 @@
       <c r="E56" s="17" t="n"/>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>쎄트렉아이  (편출)</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-1352190082</v>
+        <v>-1484448090</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>0.49%→0.00%</t>
+          <t>0.54%→0.00%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">

--- a/reports/pdf_rolling5_20261016.xlsx
+++ b/reports/pdf_rolling5_20261016.xlsx
@@ -1380,23 +1380,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-378760292</v>
+        <v>-469139514</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.57%</t>
+          <t>0.18%→0.11%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>88→76</t>
+          <t>24→12</t>
         </is>
       </c>
     </row>
@@ -1408,23 +1408,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-469139514</v>
+        <v>-378760292</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.18%→0.11%</t>
+          <t>0.58%→0.57%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>24→12</t>
+          <t>88→76</t>
         </is>
       </c>
     </row>
@@ -1492,23 +1492,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-387084694</v>
+        <v>-1883395956</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.24%</t>
+          <t>2.79%→2.62%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>48→41</t>
         </is>
       </c>
     </row>
@@ -1520,23 +1520,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-768619786</v>
+        <v>-387084694</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>1.27%→1.15%</t>
+          <t>0.33%→0.24%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>
@@ -1548,23 +1548,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-1883395956</v>
+        <v>-768619786</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>2.79%→2.62%</t>
+          <t>1.27%→1.15%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>48→41</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -2362,18 +2362,18 @@
       <c r="E55" s="17" t="n"/>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>쎄트렉아이  (편출)</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-1352190082</v>
+        <v>-1484448090</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.49%→0.00%</t>
+          <t>0.54%→0.00%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2390,18 +2390,18 @@
       <c r="E56" s="17" t="n"/>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>쎄트렉아이  (편출)</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-1484448090</v>
+        <v>-1352190082</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>0.54%→0.00%</t>
+          <t>0.49%→0.00%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -3183,23 +3183,23 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B81" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>39697476</v>
+        <v>71522457</v>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>2.62%→2.78%</t>
+          <t>1.04%→1.32%</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>86→91</t>
+          <t>19→24</t>
         </is>
       </c>
       <c r="G81" s="14" t="inlineStr">
@@ -3227,23 +3227,23 @@
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B82" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>71522457</v>
+        <v>39697476</v>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>1.04%→1.32%</t>
+          <t>2.62%→2.78%</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr">
         <is>
-          <t>19→24</t>
+          <t>86→91</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20261016.xlsx
+++ b/reports/pdf_rolling5_20261016.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,10 +62,6 @@
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -132,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -175,7 +171,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +562,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-10-08 ~ 2026-10-16  (최근 5거래일)  ·  캡처 6/7  ·  대기: RISE</t>
+          <t>최근 5거래일 변화  ·  2026-10-08 ~ 2026-10-16  (최근 5거래일)  ·  캡처 5/10  ·  대기: RISE, TIGER, DS, TIGER, MIDAS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,418억   ·   현금 410억(8.9%)      오늘 2026-10-16  vs  5일전 2026-10-08      매수 13종목  /  매도 30종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,418억      오늘 2026-10-16  vs  5일전 2026-10-08      매수 13종목  /  매도 30종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1352,23 +1347,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-746817781</v>
+        <v>-378760292</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.31%→0.13%</t>
+          <t>0.58%→0.57%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>21→9</t>
+          <t>88→76</t>
         </is>
       </c>
     </row>
@@ -1380,23 +1375,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-469139514</v>
+        <v>-746817781</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.18%→0.11%</t>
+          <t>0.31%→0.13%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>24→12</t>
+          <t>21→9</t>
         </is>
       </c>
     </row>
@@ -1408,23 +1403,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-378760292</v>
+        <v>-469139514</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.57%</t>
+          <t>0.18%→0.11%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>88→76</t>
+          <t>24→12</t>
         </is>
       </c>
     </row>
@@ -1492,23 +1487,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1883395956</v>
+        <v>-387084694</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>2.79%→2.62%</t>
+          <t>0.33%→0.24%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>48→41</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>
@@ -1520,23 +1515,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-387084694</v>
+        <v>-768619786</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.24%</t>
+          <t>1.27%→1.15%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1548,23 +1543,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-768619786</v>
+        <v>-1883395956</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>1.27%→1.15%</t>
+          <t>2.79%→2.62%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>48→41</t>
         </is>
       </c>
     </row>
@@ -1576,23 +1571,23 @@
       <c r="E31" s="17" t="n"/>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론  (편출)</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H31" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-301462273</v>
+        <v>-1215957294</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>0.06%→0.00%</t>
+          <t>0.50%→0.24%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>6→0</t>
+          <t>11→5</t>
         </is>
       </c>
     </row>
@@ -1604,23 +1599,23 @@
       <c r="E32" s="17" t="n"/>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>하나마이크론  (편출)</t>
         </is>
       </c>
       <c r="H32" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-1215957294</v>
+        <v>-301462273</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>0.50%→0.24%</t>
+          <t>0.06%→0.00%</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
         <is>
-          <t>11→5</t>
+          <t>6→0</t>
         </is>
       </c>
     </row>
@@ -1660,23 +1655,23 @@
       <c r="E34" s="17" t="n"/>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-1027171749</v>
+        <v>-366570989</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.16%</t>
+          <t>5.50%→5.22%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>5→2</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
@@ -1688,30 +1683,30 @@
       <c r="E35" s="17" t="n"/>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-366570989</v>
+        <v>-1027171749</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>5.50%→5.22%</t>
+          <t>0.41%→0.16%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>5→2</t>
         </is>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,871억   ·   현금 132억(4.5%)      오늘 2026-10-16  vs  5일전 2026-10-08      매수 2종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,871억      오늘 2026-10-16  vs  5일전 2026-10-08      매수 2종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1916,7 +1911,7 @@
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,260억   ·   현금 77억(3.4%)      오늘 2026-10-16  vs  5일전 2026-10-08      매수 8종목  /  매도 12종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,260억      오늘 2026-10-16  vs  5일전 2026-10-08      매수 8종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B44" s="4" t="n"/>
@@ -2362,18 +2357,18 @@
       <c r="E55" s="17" t="n"/>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>쎄트렉아이  (편출)</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-1484448090</v>
+        <v>-1352190082</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.54%→0.00%</t>
+          <t>0.49%→0.00%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2390,18 +2385,18 @@
       <c r="E56" s="17" t="n"/>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>쎄트렉아이  (편출)</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-1352190082</v>
+        <v>-1484448090</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>0.49%→0.00%</t>
+          <t>0.54%→0.00%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2469,7 +2464,7 @@
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,855억   ·   현금 81억(4.3%)      오늘 2026-10-16  vs  5일전 2026-10-08      매수 5종목  /  매도 10종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,855억      오늘 2026-10-16  vs  5일전 2026-10-08      매수 5종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B60" s="4" t="n"/>
@@ -2918,7 +2913,7 @@
     <row r="74" ht="19" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 263억   ·   현금 7억(2.5%)      오늘 2026-10-16  vs  5일전 2026-10-08      매수 6종목  /  매도 6종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 263억      오늘 2026-10-16  vs  5일전 2026-10-08      매수 6종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B74" s="4" t="n"/>
@@ -3183,23 +3178,23 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B81" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>71522457</v>
+        <v>39697476</v>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>1.04%→1.32%</t>
+          <t>2.62%→2.78%</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>19→24</t>
+          <t>86→91</t>
         </is>
       </c>
       <c r="G81" s="14" t="inlineStr">
@@ -3227,23 +3222,23 @@
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B82" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>39697476</v>
+        <v>71522457</v>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>2.62%→2.78%</t>
+          <t>1.04%→1.32%</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr">
         <is>
-          <t>86→91</t>
+          <t>19→24</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -3286,41 +3281,87 @@
       <c r="K84" s="19" t="n"/>
     </row>
     <row r="86" ht="19" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 994억      오늘 2026-10-16  vs  5일전 2026-10-08      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="n"/>
-      <c r="C86" s="4" t="n"/>
-      <c r="D86" s="4" t="n"/>
-      <c r="E86" s="4" t="n"/>
-      <c r="F86" s="4" t="n"/>
-      <c r="G86" s="4" t="n"/>
-      <c r="H86" s="4" t="n"/>
-      <c r="I86" s="4" t="n"/>
-      <c r="J86" s="4" t="n"/>
-      <c r="K86" s="4" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="20" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
+      <c r="A86" s="18" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B86" s="19" t="n"/>
+      <c r="C86" s="19" t="n"/>
+      <c r="D86" s="19" t="n"/>
+      <c r="E86" s="19" t="n"/>
+      <c r="F86" s="19" t="n"/>
+      <c r="G86" s="19" t="n"/>
+      <c r="H86" s="19" t="n"/>
+      <c r="I86" s="19" t="n"/>
+      <c r="J86" s="19" t="n"/>
+      <c r="K86" s="19" t="n"/>
+    </row>
+    <row r="88" ht="19" customHeight="1">
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t>■ DS 코스닥액티브  (DS)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B88" s="19" t="n"/>
+      <c r="C88" s="19" t="n"/>
+      <c r="D88" s="19" t="n"/>
+      <c r="E88" s="19" t="n"/>
+      <c r="F88" s="19" t="n"/>
+      <c r="G88" s="19" t="n"/>
+      <c r="H88" s="19" t="n"/>
+      <c r="I88" s="19" t="n"/>
+      <c r="J88" s="19" t="n"/>
+      <c r="K88" s="19" t="n"/>
+    </row>
+    <row r="90" ht="19" customHeight="1">
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B90" s="19" t="n"/>
+      <c r="C90" s="19" t="n"/>
+      <c r="D90" s="19" t="n"/>
+      <c r="E90" s="19" t="n"/>
+      <c r="F90" s="19" t="n"/>
+      <c r="G90" s="19" t="n"/>
+      <c r="H90" s="19" t="n"/>
+      <c r="I90" s="19" t="n"/>
+      <c r="J90" s="19" t="n"/>
+      <c r="K90" s="19" t="n"/>
+    </row>
+    <row r="92" ht="19" customHeight="1">
+      <c r="A92" s="18" t="inlineStr">
+        <is>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B92" s="19" t="n"/>
+      <c r="C92" s="19" t="n"/>
+      <c r="D92" s="19" t="n"/>
+      <c r="E92" s="19" t="n"/>
+      <c r="F92" s="19" t="n"/>
+      <c r="G92" s="19" t="n"/>
+      <c r="H92" s="19" t="n"/>
+      <c r="I92" s="19" t="n"/>
+      <c r="J92" s="19" t="n"/>
+      <c r="K92" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
+    <mergeCell ref="A92:K92"/>
     <mergeCell ref="A45:E45"/>
     <mergeCell ref="A60:K60"/>
     <mergeCell ref="A61:E61"/>
     <mergeCell ref="G61:K61"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="G75:K75"/>
-    <mergeCell ref="A87:K87"/>
+    <mergeCell ref="A88:K88"/>
     <mergeCell ref="G38:K38"/>
     <mergeCell ref="A75:E75"/>
     <mergeCell ref="A84:K84"/>
+    <mergeCell ref="A90:K90"/>
     <mergeCell ref="A37:K37"/>
     <mergeCell ref="A74:K74"/>
     <mergeCell ref="A3:K3"/>

--- a/reports/pdf_rolling5_20261016.xlsx
+++ b/reports/pdf_rolling5_20261016.xlsx
@@ -1347,23 +1347,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-378760292</v>
+        <v>-469139514</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.57%</t>
+          <t>0.18%→0.11%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>88→76</t>
+          <t>24→12</t>
         </is>
       </c>
     </row>
@@ -1403,23 +1403,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-469139514</v>
+        <v>-378760292</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.18%→0.11%</t>
+          <t>0.58%→0.57%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>24→12</t>
+          <t>88→76</t>
         </is>
       </c>
     </row>
@@ -1515,23 +1515,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-768619786</v>
+        <v>-1883395956</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>1.27%→1.15%</t>
+          <t>2.79%→2.62%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>48→41</t>
         </is>
       </c>
     </row>
@@ -1543,23 +1543,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-1883395956</v>
+        <v>-768619786</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>2.79%→2.62%</t>
+          <t>1.27%→1.15%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>48→41</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1655,23 +1655,23 @@
       <c r="E34" s="17" t="n"/>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-366570989</v>
+        <v>-1027171749</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>5.50%→5.22%</t>
+          <t>0.41%→0.16%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>5→2</t>
         </is>
       </c>
     </row>
@@ -1683,23 +1683,23 @@
       <c r="E35" s="17" t="n"/>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-1027171749</v>
+        <v>-366570989</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.16%</t>
+          <t>5.50%→5.22%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>5→2</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
@@ -2220,23 +2220,23 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>744329645</v>
+        <v>1110967268</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>2.82%→3.42%</t>
+          <t>1.95%→3.18%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>129→143</t>
+          <t>75→89</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -2264,23 +2264,23 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>1110967268</v>
+        <v>744329645</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>1.95%→3.18%</t>
+          <t>2.82%→3.42%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>75→89</t>
+          <t>129→143</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -3178,23 +3178,23 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B81" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>39697476</v>
+        <v>71522457</v>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>2.62%→2.78%</t>
+          <t>1.04%→1.32%</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>86→91</t>
+          <t>19→24</t>
         </is>
       </c>
       <c r="G81" s="14" t="inlineStr">
@@ -3222,23 +3222,23 @@
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B82" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>71522457</v>
+        <v>39697476</v>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>1.04%→1.32%</t>
+          <t>2.62%→2.78%</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr">
         <is>
-          <t>19→24</t>
+          <t>86→91</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
